--- a/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas</t>
+          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +638,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,78</t>
+          <t>1,32; 4,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,7</t>
+          <t>2,72; 5,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,01</t>
+          <t>1,9; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 11,62</t>
+          <t>4,67; 12,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,54</t>
+          <t>1,85; 7,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,21</t>
+          <t>1,47; 2,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,56</t>
+          <t>1,61; 3,49</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,29 +756,29 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 5,35</t>
+          <t>1,93; 5,28</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,05; 3,75</t>
+          <t>2,08; 3,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,3</t>
+          <t>1,97; 3,29</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 9,24</t>
+          <t>3,66; 9,18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +856,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,08</t>
+          <t>3,1; 6,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,3</t>
+          <t>2,02; 5,58</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,68</t>
+          <t>1,83; 5,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 4,34</t>
+          <t>1,76; 4,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,92</t>
+          <t>1,78; 2,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 5,31</t>
+          <t>2,48; 5,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,15</t>
+          <t>2,86; 5,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 5,1</t>
+          <t>2,25; 4,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 5,03</t>
+          <t>2,68; 4,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,55</t>
+          <t>2,45; 4,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,61</t>
+          <t>2,5; 4,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,14</t>
+          <t>2,31; 4,24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,1</t>
+          <t>2,43; 7,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,39</t>
+          <t>2,83; 5,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,19</t>
+          <t>1,0; 4,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,7</t>
+          <t>1,71; 5,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,37</t>
+          <t>1,44; 2,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 8,71</t>
+          <t>1,44; 8,8</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,55</t>
+          <t>2,49; 5,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,59</t>
+          <t>1,61; 3,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,99</t>
+          <t>2,27; 3,99</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,52</t>
+          <t>1,0; 1,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,05</t>
+          <t>3,33; 7,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 8,83</t>
+          <t>2,77; 9,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,3</t>
+          <t>2,96; 6,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,15</t>
+          <t>1,57; 6,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,09</t>
+          <t>1,93; 5,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,42</t>
+          <t>2,12; 3,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,9</t>
+          <t>4,46; 10,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,23</t>
+          <t>1,39; 4,53</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,09</t>
+          <t>3,05; 6,15</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,51</t>
+          <t>2,65; 5,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,39; 8,7</t>
+          <t>4,24; 8,83</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,72</t>
+          <t>2,63; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,55</t>
+          <t>3,21; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,37</t>
+          <t>3,78; 8,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,34 +1311,34 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,48; 9,19</t>
+          <t>4,36; 9,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,0</t>
+          <t>1,0; 6,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 6,02</t>
+          <t>3,33; 5,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,65</t>
+          <t>2,09; 4,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 7,19</t>
+          <t>4,17; 7,21</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,09</t>
+          <t>1,2; 14,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,86</t>
+          <t>1,41; 4,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,23</t>
+          <t>2,32; 6,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 11,06</t>
+          <t>1,73; 10,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 5,65</t>
+          <t>1,75; 5,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,06</t>
+          <t>2,95; 6,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 9,61</t>
+          <t>1,63; 8,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,5</t>
+          <t>1,9; 4,43</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,14 +1471,14 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,56</t>
+          <t>3,0; 5,47</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 7,75</t>
+          <t>2,39; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,5</t>
+          <t>1,49; 5,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,69</t>
+          <t>1,71; 4,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,38</t>
+          <t>3,22; 5,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,16</t>
+          <t>1,0; 11,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,88</t>
+          <t>1,14; 1,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,91</t>
+          <t>1,15; 3,88</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,64</t>
+          <t>4,57; 8,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 7,04</t>
+          <t>2,29; 7,0</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,0</t>
+          <t>1,53; 4,03</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,02</t>
+          <t>1,68; 3,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,29; 6,84</t>
+          <t>4,35; 6,87</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,77; 5,92</t>
+          <t>2,72; 5,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,82</t>
+          <t>1,72; 3,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,82</t>
+          <t>2,36; 5,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,29</t>
+          <t>3,56; 7,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,49</t>
+          <t>4,77; 7,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,5; 8,41</t>
+          <t>3,66; 8,65</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,15; 6,54</t>
+          <t>2,04; 7,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 7,85</t>
+          <t>4,14; 7,97</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,58</t>
+          <t>4,46; 6,6</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,56</t>
+          <t>3,06; 6,3</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,26</t>
+          <t>2,65; 5,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 7,29</t>
+          <t>4,55; 7,54</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,75</t>
+          <t>2,96; 4,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,87; 4,2</t>
+          <t>2,94; 4,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,25</t>
+          <t>2,65; 4,23</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,71; 4,98</t>
+          <t>3,69; 4,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,05</t>
+          <t>3,18; 4,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,99; 4,39</t>
+          <t>2,98; 4,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,54; 3,82</t>
+          <t>2,58; 4,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,12</t>
+          <t>4,42; 6,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,23; 4,49</t>
+          <t>3,26; 4,46</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,11; 4,04</t>
+          <t>3,08; 4,07</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,76</t>
+          <t>2,76; 3,84</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 5,35</t>
+          <t>4,24; 5,38</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el número de días que limitaron su actividad por dolores o síntomas (tasa de respuesta: 97,76%)</t>
+          <t>Tiempo medio en días que limitaron su actividad en las últimas 2 semanas por dolores o síntomas (tasa de respuesta: 97,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,56</t>
+          <t>1,35; 4,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,94</t>
+          <t>2,72; 5,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,09</t>
+          <t>1,89; 4,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,67; 12,48</t>
+          <t>5,0; 12,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,42</t>
+          <t>1,84; 6,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,23</t>
+          <t>1,42; 2,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,49</t>
+          <t>1,64; 3,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -756,22 +756,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,28</t>
+          <t>1,9; 5,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,95</t>
+          <t>2,1; 3,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,97; 3,29</t>
+          <t>2,0; 3,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,66; 9,18</t>
+          <t>3,93; 9,33</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 6,14</t>
+          <t>3,17; 6,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 5,58</t>
+          <t>1,91; 5,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,66</t>
+          <t>1,85; 6,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,3</t>
+          <t>1,82; 4,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,96</t>
+          <t>1,75; 2,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 5,44</t>
+          <t>2,41; 5,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,12</t>
+          <t>2,87; 5,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,96</t>
+          <t>2,29; 4,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 4,92</t>
+          <t>2,79; 4,76</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,46</t>
+          <t>2,45; 4,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,6</t>
+          <t>2,49; 4,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,24</t>
+          <t>2,29; 4,1</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,2</t>
+          <t>2,38; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 5,44</t>
+          <t>2,75; 5,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 5,68</t>
+          <t>1,9; 5,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 2,38</t>
+          <t>1,43; 2,39</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 8,8</t>
+          <t>1,85; 8,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 5,46</t>
+          <t>2,44; 5,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,99</t>
+          <t>2,32; 4,07</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,53</t>
+          <t>1,0; 1,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,49</t>
+          <t>3,23; 7,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 9,06</t>
+          <t>2,76; 8,6</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,49</t>
+          <t>2,91; 6,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 6,41</t>
+          <t>1,55; 6,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,94</t>
+          <t>1,99; 6,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,4</t>
+          <t>2,17; 3,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,61</t>
+          <t>4,1; 10,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,53</t>
+          <t>1,38; 4,45</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,15</t>
+          <t>3,07; 5,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,99</t>
+          <t>2,64; 6,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,24; 8,83</t>
+          <t>4,2; 8,89</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,69</t>
+          <t>2,64; 4,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,85</t>
+          <t>1,87; 5,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,59</t>
+          <t>3,18; 5,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,41</t>
+          <t>3,74; 8,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,27 +1311,27 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,17</t>
+          <t>4,76; 9,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,0</t>
+          <t>1,61; 6,0</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,86</t>
+          <t>3,29; 5,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,62</t>
+          <t>2,09; 5,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 7,21</t>
+          <t>4,16; 7,21</t>
         </is>
       </c>
     </row>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,87</t>
+          <t>1,41; 5,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,48</t>
+          <t>2,08; 6,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,14</t>
+          <t>1,73; 11,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 6,17</t>
+          <t>2,86; 5,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,53</t>
+          <t>1,69; 8,88</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,43</t>
+          <t>1,85; 4,47</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 5,47</t>
+          <t>2,93; 5,47</t>
         </is>
       </c>
     </row>
@@ -1556,22 +1556,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 7,46</t>
+          <t>2,48; 7,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,48</t>
+          <t>1,49; 5,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,58</t>
+          <t>1,69; 4,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,44</t>
+          <t>3,34; 5,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1581,37 +1581,37 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,84</t>
+          <t>1,14; 1,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,88</t>
+          <t>1,15; 3,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,75</t>
+          <t>4,42; 8,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 7,0</t>
+          <t>2,33; 6,66</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,03</t>
+          <t>1,52; 3,91</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,7</t>
+          <t>1,7; 3,71</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,35; 6,87</t>
+          <t>4,25; 6,85</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,93</t>
+          <t>2,72; 5,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,83</t>
+          <t>1,72; 4,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,8</t>
+          <t>2,47; 5,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,56; 7,31</t>
+          <t>3,47; 7,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,47</t>
+          <t>4,79; 7,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,65</t>
+          <t>3,51; 8,49</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,28</t>
+          <t>2,08; 6,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,97</t>
+          <t>4,1; 8,06</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,46; 6,6</t>
+          <t>4,44; 6,55</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,06; 6,3</t>
+          <t>3,02; 6,17</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,48</t>
+          <t>2,6; 5,31</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,54</t>
+          <t>4,58; 7,41</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,68</t>
+          <t>2,83; 4,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,94; 4,17</t>
+          <t>2,89; 4,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,23</t>
+          <t>2,67; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,95</t>
+          <t>3,67; 4,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,91</t>
+          <t>3,22; 4,91</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,42</t>
+          <t>2,97; 4,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,0</t>
+          <t>2,53; 3,89</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,1</t>
+          <t>4,36; 6,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,26; 4,46</t>
+          <t>3,29; 4,58</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,08; 4,07</t>
+          <t>3,12; 4,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,84</t>
+          <t>2,76; 3,83</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,38</t>
+          <t>4,24; 5,41</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ12A-Provincia-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>3,52</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,39</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,81</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>2,33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,71</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7,34</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,39</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,85</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>6,63</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,95</t>
+          <t>1,84; 7,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,91</t>
+          <t>1,45; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,13</t>
+          <t>1,65; 3,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,04</t>
+          <t>2,0; 9,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,84; 6,87</t>
+          <t>1,34; 4,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,22</t>
+          <t>2,73; 5,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,66</t>
+          <t>1,91; 4,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 9,16</t>
+          <t>4,82; 11,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,37</t>
+          <t>1,92; 5,35</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,89</t>
+          <t>2,05; 3,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 3,38</t>
+          <t>1,96; 3,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,93; 9,33</t>
+          <t>3,91; 9,37</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3,47</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3,85</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3,54</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,33</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,15</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,72</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,31</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>3,47</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,85</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>2,71</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,05</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,02</t>
+          <t>1,63; 2,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,4</t>
+          <t>2,37; 5,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,33</t>
+          <t>2,87; 5,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,17</t>
+          <t>2,25; 5,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,94</t>
+          <t>3,17; 6,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,41; 5,26</t>
+          <t>1,82; 5,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,14</t>
+          <t>1,81; 5,68</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,89</t>
+          <t>1,77; 4,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,76</t>
+          <t>2,81; 5,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,55</t>
+          <t>2,5; 4,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,59</t>
+          <t>2,51; 4,61</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,1</t>
+          <t>2,26; 4,19</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,81</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,99</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1,87</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,72</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,63</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>4,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,81</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,19</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,99</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>4,11</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,08</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,0; 4,19</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1,79; 5,7</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 4,0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,35; 2,37</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>1,0; 13,01</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2,38; 7,38</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2,38; 7,1</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
         <is>
           <t>1,0; 3,63</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,75; 5,53</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 4,2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,9; 5,77</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,0; 4,0</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,43; 2,39</t>
+          <t>2,85; 5,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 8,48</t>
+          <t>1,45; 8,71</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 5,49</t>
+          <t>2,44; 5,55</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,59</t>
+          <t>1,56; 3,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,07</t>
+          <t>2,36; 4,11</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2,83</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3,68</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6,96</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4,96</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,67</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,68</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,91</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,0</t>
+          <t>5,89</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,54</t>
+          <t>1,56; 7,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,41</t>
+          <t>1,92; 6,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,76; 8,6</t>
+          <t>2,11; 3,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,52</t>
+          <t>4,31; 10,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,44</t>
+          <t>1,0; 1,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,21</t>
+          <t>3,11; 7,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,43</t>
+          <t>2,7; 8,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,89</t>
+          <t>2,92; 6,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,45</t>
+          <t>1,38; 4,23</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,07; 5,96</t>
+          <t>3,11; 6,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 6,11</t>
+          <t>2,69; 5,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 8,89</t>
+          <t>4,24; 8,56</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,0</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>7,23</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>1,93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>3,27</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,22</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,0</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,29</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,86</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,17</t>
+          <t>4,21</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3,75; 8,37</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2,0; 7,0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4,48; 9,22</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1,0; 3,0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2,64; 4,98</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1,87; 5,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3,18; 5,54</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,46</t>
+          <t>2,64; 4,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 7,0</t>
+          <t>1,87; 4,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 9,45</t>
+          <t>3,19; 5,49</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,78</t>
+          <t>3,31; 6,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,03</t>
+          <t>2,01; 4,65</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,16; 7,21</t>
+          <t>4,27; 7,2</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,21</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3,44</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5,03</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>4,07</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>4,29</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2,41</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2,0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,21</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,44</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,03</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,17</t>
+          <t>4,13</t>
         </is>
       </c>
     </row>
@@ -1416,52 +1416,52 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 14,0</t>
+          <t>1,73; 11,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,01</t>
+          <t>1,76; 5,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>1,0; 10,0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2,73; 5,93</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1,0; 11,09</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1,41; 4,86</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2,08; 6,39</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>1,73; 11,12</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,75; 5,41</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>1,0; 10,0</t>
-        </is>
-      </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,95</t>
+          <t>2,36; 6,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,88</t>
+          <t>1,63; 9,61</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,47</t>
+          <t>1,9; 4,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,47</t>
+          <t>3,06; 5,49</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2,02</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6,11</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>4,26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,79</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,27</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,49</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,5</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,02</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>6,17</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,28</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 7,72</t>
+          <t>1,0; 11,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,39</t>
+          <t>1,14; 1,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,58</t>
+          <t>1,15; 3,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,34; 5,55</t>
+          <t>4,47; 8,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 11,42</t>
+          <t>2,56; 7,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 1,81</t>
+          <t>1,58; 5,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,65</t>
+          <t>1,71; 4,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,66</t>
+          <t>3,21; 5,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,66</t>
+          <t>2,33; 7,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,91</t>
+          <t>1,53; 4,0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,71</t>
+          <t>1,75; 4,02</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,85</t>
+          <t>4,25; 6,79</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5,85</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>5,5</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,81</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>6,47</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>4,13</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>2,38</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>3,65</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>5,6</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>5,85</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,5</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,81</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>5,61</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,01</t>
+          <t>6,23</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,68</t>
+          <t>4,74; 7,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,03</t>
+          <t>3,5; 8,41</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 5,88</t>
+          <t>2,15; 6,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,38</t>
+          <t>4,23; 8,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,79; 7,58</t>
+          <t>2,77; 5,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,51; 8,49</t>
+          <t>1,71; 3,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,86</t>
+          <t>2,4; 5,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,06</t>
+          <t>3,45; 7,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,55</t>
+          <t>4,46; 6,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,02; 6,17</t>
+          <t>3,08; 6,56</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,31</t>
+          <t>2,59; 5,26</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,41</t>
+          <t>4,64; 7,51</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,95</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3,59</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5,29</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,66</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>3,46</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>3,26</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,95</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,59</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>3,13</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5,18</t>
+          <t>4,2</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4,78</t>
+          <t>4,8</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,75</t>
+          <t>3,22; 5,05</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,89; 4,18</t>
+          <t>2,99; 4,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,67; 4,15</t>
+          <t>2,54; 3,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,67; 4,92</t>
+          <t>4,49; 6,23</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,91</t>
+          <t>2,94; 4,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,97; 4,38</t>
+          <t>2,87; 4,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,89</t>
+          <t>2,65; 4,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,11</t>
+          <t>3,63; 4,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,29; 4,58</t>
+          <t>3,23; 4,49</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3,12; 4,04</t>
+          <t>3,11; 4,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 3,83</t>
+          <t>2,77; 3,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>4,24; 5,41</t>
+          <t>4,25; 5,38</t>
         </is>
       </c>
     </row>
